--- a/Assets/06 Data/ExcelData/Enemy_Table.xlsx
+++ b/Assets/06 Data/ExcelData/Enemy_Table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\덕코프 기획\데이터테이블\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\StudyUnity\Duckov\Assets\06 Data\ExcelData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489CDA0D-D822-4892-8CA0-002D831DE4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC182680-3B7B-445C-9EFE-08D8750ADA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30030" yWindow="3465" windowWidth="18225" windowHeight="7140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>maxHP</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>걷기 속도</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -51,22 +47,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>runSpeed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>walkSpeed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>순찰 반경</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>patrolRange</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>소리 감지 레벨</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -79,15 +63,31 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>soundDetectionLevel</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>viewRange</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>viewAngel</t>
+    <t>MaxHP</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WalkSpeed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RunSpeed</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PatrolRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SoundDetectionLevel</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ViewRange</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ViewAngle</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -498,36 +498,36 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>13</v>
